--- a/results/tab/trait_trait_mixed_ALL_LEAVES_model_outputs_raw_GLOBAL.xlsx
+++ b/results/tab/trait_trait_mixed_ALL_LEAVES_model_outputs_raw_GLOBAL.xlsx
@@ -1,21 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rbgkew-my.sharepoint.com/personal/j_white2_kew_org/Documents/Documents/research/colabs/drakensberg_grasslands_functional_traits/results/tab/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2E6DFDCE8F79A8D366075C52F3FE2AB6F9759013" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C088FD8-8B22-4C59-B21A-81B3F143466A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>trait_x</t>
+  </si>
+  <si>
+    <t>trait_x^2</t>
+  </si>
+  <si>
+    <t>SD (Intercept species)</t>
+  </si>
+  <si>
+    <t>SD (trait_x species)</t>
+  </si>
+  <si>
+    <t>Cor (Intercept~trait_x species)</t>
+  </si>
+  <si>
+    <t>SD (Observations)</t>
+  </si>
+  <si>
+    <t>Num.Obs.</t>
+  </si>
+  <si>
+    <t>R2 Marg.</t>
+  </si>
+  <si>
+    <t>R2 Cond.</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>ICC</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>A. leaf thickness~sla (linear)</t>
+  </si>
+  <si>
+    <t>0.428 [0.369, 0.488] ***</t>
+  </si>
+  <si>
+    <t>-0.218 [-0.284, -0.152] ***</t>
+  </si>
+  <si>
+    <t>0.226</t>
+  </si>
+  <si>
+    <t>0.198</t>
+  </si>
+  <si>
+    <t>-0.814</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>2499</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>0.736</t>
+  </si>
+  <si>
+    <t>-4037.2</t>
+  </si>
+  <si>
+    <t>-4002.3</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>B. ldmc~sla (polynomial)</t>
+  </si>
+  <si>
+    <t>0.545 [0.494, 0.595] ***</t>
+  </si>
+  <si>
+    <t>-0.193 [-0.300, -0.086] ***</t>
+  </si>
+  <si>
+    <t>-0.123 [-0.211, -0.034] **</t>
+  </si>
+  <si>
+    <t>0.173</t>
+  </si>
+  <si>
+    <t>0.164</t>
+  </si>
+  <si>
+    <t>-0.421</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>0.871</t>
+  </si>
+  <si>
+    <t>-6114.3</t>
+  </si>
+  <si>
+    <t>-6073.5</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>C. ldmc~leaf thickness (linear)</t>
+  </si>
+  <si>
+    <t>0.457 [0.415, 0.500] ***</t>
+  </si>
+  <si>
+    <t>-0.095 [-0.149, -0.041] ***</t>
+  </si>
+  <si>
+    <t>0.165</t>
+  </si>
+  <si>
+    <t>0.132</t>
+  </si>
+  <si>
+    <t>-0.300</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>0.830</t>
+  </si>
+  <si>
+    <t>-5600.1</t>
+  </si>
+  <si>
+    <t>-5565.1</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +242,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +294,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +328,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +363,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,306 +539,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>trait_x</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>trait_x^2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SD (Intercept species)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SD (trait_x species)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cor (Intercept~trait_x species)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>SD (Observations)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Num.Obs.</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>R2 Marg.</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>R2 Cond.</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ICC</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A. leaf thickness~sla (linear)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.428 [0.369, 0.488] ***</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>-0.218 [-0.284, -0.152] ***</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.226</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.198</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-0.814</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.101</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.736</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-4037.2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-4002.3</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B. ldmc~sla (polynomial)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.545 [0.494, 0.595] ***</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-0.193 [-0.300, -0.086] ***</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-0.123 [-0.211, -0.034] **</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.173</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-0.421</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.065</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.871</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-6114.3</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-6073.5</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C. ldmc~leaf thickness (linear)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.457 [0.415, 0.500] ***</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>-0.095 [-0.149, -0.041] ***</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.165</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.132</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-0.300</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.073</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.014</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.830</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-5600.1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-5565.1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
